--- a/AAII_Financials/Quarterly/BTCT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BTCT_QTR_FIN.xlsx
@@ -2461,10 +2461,10 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="F42" s="3">
         <v>1200</v>
@@ -2638,10 +2638,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>12100</v>
+        <v>8700</v>
       </c>
       <c r="E45" s="3">
-        <v>12100</v>
+        <v>8700</v>
       </c>
       <c r="F45" s="3">
         <v>8100</v>
